--- a/Extracted_data_analysis/global/Output-Transformed_data/eco_reg_tot.xlsx
+++ b/Extracted_data_analysis/global/Output-Transformed_data/eco_reg_tot.xlsx
@@ -543,7 +543,7 @@
         <v>20072</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1038,7 +1038,7 @@
         <v>20029</v>
       </c>
       <c r="K15">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -2838,7 +2838,7 @@
         <v>20224</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -6168,7 +6168,7 @@
         <v>20087</v>
       </c>
       <c r="K129">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="130">
@@ -9453,7 +9453,7 @@
         <v>20100</v>
       </c>
       <c r="K202">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="203">
@@ -9903,7 +9903,7 @@
         <v>20143</v>
       </c>
       <c r="K212">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="213">
@@ -10218,7 +10218,7 @@
         <v>20018</v>
       </c>
       <c r="K219">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="220">
@@ -10308,7 +10308,7 @@
         <v>20065</v>
       </c>
       <c r="K221">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="222">
@@ -10803,7 +10803,7 @@
         <v>25035</v>
       </c>
       <c r="K232">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="233">
